--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -9957,7 +9957,7 @@
         <v>117780812</v>
       </c>
       <c r="B81" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -10174,10 +10174,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118378548</v>
+        <v>118377997</v>
       </c>
       <c r="B83" t="n">
-        <v>100801</v>
+        <v>97062</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10186,25 +10186,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1478</v>
+        <v>222759</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446870</v>
+        <v>446813</v>
       </c>
       <c r="R83" t="n">
-        <v>7180413</v>
+        <v>7180423</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118377997</v>
+        <v>118378004</v>
       </c>
       <c r="B84" t="n">
-        <v>97062</v>
+        <v>78838</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10288,25 +10288,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222759</v>
+        <v>1321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Klot-tegellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Psora globifera</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) A.Massal.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446813</v>
+        <v>446886</v>
       </c>
       <c r="R84" t="n">
-        <v>7180423</v>
+        <v>7180480</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10354,6 +10354,11 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>1 kv.dm inom en halv kvadratmeterruta</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10362,6 +10367,11 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>brant lodyta mot SO</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10378,10 +10388,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118378004</v>
+        <v>118378548</v>
       </c>
       <c r="B85" t="n">
-        <v>78838</v>
+        <v>100801</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10390,25 +10400,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1321</v>
+        <v>1478</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klot-tegellav</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Psora globifera</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10418,10 +10428,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446886</v>
+        <v>446870</v>
       </c>
       <c r="R85" t="n">
-        <v>7180480</v>
+        <v>7180413</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10456,11 +10466,6 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>1 kv.dm inom en halv kvadratmeterruta</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10469,11 +10474,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>brant lodyta mot SO</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -10061,10 +10061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118377994</v>
+        <v>118377997</v>
       </c>
       <c r="B82" t="n">
-        <v>79520</v>
+        <v>97062</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10073,25 +10073,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229487</v>
+        <v>222759</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällgytterlav</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pannaria hookeri</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Borrer ex Sm.) Nyl.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10101,10 +10101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446804</v>
+        <v>446813</v>
       </c>
       <c r="R82" t="n">
-        <v>7180398</v>
+        <v>7180423</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10139,25 +10139,14 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>12 bålar</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>stenhäll</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10174,10 +10163,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118377997</v>
+        <v>118378004</v>
       </c>
       <c r="B83" t="n">
-        <v>97062</v>
+        <v>78838</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10186,25 +10175,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222759</v>
+        <v>1321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Klot-tegellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Psora globifera</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) A.Massal.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10214,10 +10203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446813</v>
+        <v>446886</v>
       </c>
       <c r="R83" t="n">
-        <v>7180423</v>
+        <v>7180480</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10252,6 +10241,11 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>1 kv.dm inom en halv kvadratmeterruta</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10260,6 +10254,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>brant lodyta mot SO</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10276,10 +10275,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118378004</v>
+        <v>118378548</v>
       </c>
       <c r="B84" t="n">
-        <v>78838</v>
+        <v>100801</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10288,25 +10287,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1321</v>
+        <v>1478</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klot-tegellav</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Psora globifera</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10316,10 +10315,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446886</v>
+        <v>446870</v>
       </c>
       <c r="R84" t="n">
-        <v>7180480</v>
+        <v>7180413</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10354,11 +10353,6 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>1 kv.dm inom en halv kvadratmeterruta</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10367,11 +10361,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>brant lodyta mot SO</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10388,10 +10377,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118378548</v>
+        <v>118377994</v>
       </c>
       <c r="B85" t="n">
-        <v>100801</v>
+        <v>79520</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10404,21 +10393,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1478</v>
+        <v>229487</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Fjällgytterlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Pannaria hookeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10428,10 +10417,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446870</v>
+        <v>446804</v>
       </c>
       <c r="R85" t="n">
-        <v>7180413</v>
+        <v>7180398</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10466,14 +10455,25 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>12 bålar</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>stenhäll</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -10061,10 +10061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118377997</v>
+        <v>118377994</v>
       </c>
       <c r="B82" t="n">
-        <v>97062</v>
+        <v>79527</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10073,25 +10073,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222759</v>
+        <v>229487</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Fjällgytterlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Pannaria hookeri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10101,10 +10101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446813</v>
+        <v>446804</v>
       </c>
       <c r="R82" t="n">
-        <v>7180423</v>
+        <v>7180398</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10139,14 +10139,25 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>12 bålar</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>stenhäll</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10166,7 +10177,7 @@
         <v>118378004</v>
       </c>
       <c r="B83" t="n">
-        <v>78838</v>
+        <v>78845</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10275,10 +10286,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118378548</v>
+        <v>118377997</v>
       </c>
       <c r="B84" t="n">
-        <v>100801</v>
+        <v>97069</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10287,25 +10298,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1478</v>
+        <v>222759</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10315,10 +10326,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446870</v>
+        <v>446813</v>
       </c>
       <c r="R84" t="n">
-        <v>7180413</v>
+        <v>7180423</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10377,10 +10388,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118377994</v>
+        <v>118378548</v>
       </c>
       <c r="B85" t="n">
-        <v>79520</v>
+        <v>100808</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10393,21 +10404,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229487</v>
+        <v>1478</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällgytterlav</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pannaria hookeri</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Borrer ex Sm.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10417,10 +10428,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446804</v>
+        <v>446870</v>
       </c>
       <c r="R85" t="n">
-        <v>7180398</v>
+        <v>7180413</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10455,25 +10466,14 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>12 bålar</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>stenhäll</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -10174,10 +10174,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118378004</v>
+        <v>118378548</v>
       </c>
       <c r="B83" t="n">
-        <v>78845</v>
+        <v>100808</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10186,25 +10186,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1321</v>
+        <v>1478</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Klot-tegellav</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Psora globifera</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446886</v>
+        <v>446870</v>
       </c>
       <c r="R83" t="n">
-        <v>7180480</v>
+        <v>7180413</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10252,11 +10252,6 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>1 kv.dm inom en halv kvadratmeterruta</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10265,11 +10260,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>brant lodyta mot SO</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10388,10 +10378,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118378548</v>
+        <v>118378004</v>
       </c>
       <c r="B85" t="n">
-        <v>100808</v>
+        <v>78845</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10400,25 +10390,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1478</v>
+        <v>1321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Klot-tegellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Psora globifera</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) A.Massal.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10428,10 +10418,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>446870</v>
+        <v>446886</v>
       </c>
       <c r="R85" t="n">
-        <v>7180413</v>
+        <v>7180480</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10466,6 +10456,11 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>1 kv.dm inom en halv kvadratmeterruta</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10474,6 +10469,11 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>brant lodyta mot SO</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6833,10 +6833,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>62732390</v>
+        <v>65413373</v>
       </c>
       <c r="B54" t="n">
-        <v>95717</v>
+        <v>95756</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6849,16 +6849,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220686</v>
+        <v>222759</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6867,19 +6867,22 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säterklumpen, Jmt</t>
+          <t>Raudek-området, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447792.8919043965</v>
+        <v>446783.9281718784</v>
       </c>
       <c r="R54" t="n">
-        <v>7179385.912672511</v>
+        <v>7180331.204034076</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6903,7 +6906,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>1982-08-18</t>
+          <t>2014-07-09</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -6913,7 +6916,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1982-08-18</t>
+          <t>2014-07-09</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -6929,31 +6932,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Fjälllövskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>65413373</v>
+        <v>65413380</v>
       </c>
       <c r="B55" t="n">
-        <v>95756</v>
+        <v>99201</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6962,25 +6960,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222759</v>
+        <v>1478</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6993,10 +6991,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446783.9281718784</v>
+        <v>446578.8737871609</v>
       </c>
       <c r="R55" t="n">
-        <v>7180331.204034076</v>
+        <v>7180346.364856812</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7065,7 +7063,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>65413380</v>
+        <v>72635383</v>
       </c>
       <c r="B56" t="n">
         <v>99201</v>
@@ -7098,20 +7096,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Raudek-området, Jmt</t>
+          <t>Raudekfjället, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446578.8737871609</v>
+        <v>446699.4498857252</v>
       </c>
       <c r="R56" t="n">
-        <v>7180346.364856812</v>
+        <v>7180295.099389408</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7138,7 +7149,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7148,7 +7159,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -7156,34 +7167,45 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ca 90 ex</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Översilade berghällar</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Lars Erik Norbäck</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>72635383</v>
+        <v>87754433</v>
       </c>
       <c r="B57" t="n">
-        <v>99201</v>
+        <v>77848</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7192,57 +7214,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1478</v>
+        <v>1321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Klot-tegellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Psora globifera</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>(Ach.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Raudekfjället, Jmt</t>
+          <t>Raudek, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446699.4498857252</v>
+        <v>446876.0362978961</v>
       </c>
       <c r="R57" t="n">
-        <v>7180295.099389408</v>
+        <v>7180412.034489864</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7266,7 +7275,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
@@ -7276,7 +7285,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -7286,7 +7295,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ca 90 ex</t>
+          <t>Gott om bålar på fina lerskiffärhällar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7299,30 +7308,25 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Översilade berghällar</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Fredrik Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars Erik Norbäck</t>
+          <t>Fredrik Larsson, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>87754433</v>
+        <v>87809322</v>
       </c>
       <c r="B58" t="n">
-        <v>77848</v>
+        <v>93044</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7331,44 +7335,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1321</v>
+        <v>2809</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Klot-tegellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Psora globifera</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) A.Massal.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Raudek, Jmt</t>
+          <t>Raudekfjällets SO-sluttning, 500-600 msm, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446876.0362978961</v>
+        <v>446811.1227462236</v>
       </c>
       <c r="R58" t="n">
-        <v>7180412.034489864</v>
+        <v>7180320.89791601</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7410,40 +7411,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Gott om bålar på fina lerskiffärhällar</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Larsson</t>
+          <t>Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Larsson, Tomas Hallingbäck</t>
+          <t>Tomas Hallingbäck, Fredrik Larsson, Peter Carlsson, Lars-Åke Flodin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>87809322</v>
+        <v>87809316</v>
       </c>
       <c r="B59" t="n">
-        <v>93044</v>
+        <v>92871</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7456,21 +7451,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2809</v>
+        <v>2699</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Klotuffmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Palustriella falcata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Brid.) Hedenäs</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7526,6 +7521,11 @@
       <c r="AB59" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7552,10 +7552,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87809316</v>
+        <v>87809328</v>
       </c>
       <c r="B60" t="n">
-        <v>92871</v>
+        <v>92870</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7568,21 +7568,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Klotuffmossa</t>
+          <t>Nordlig tuffmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Palustriella falcata</t>
+          <t>Palustriella decipiens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brid.) Hedenäs</t>
+          <t>(De Not.) Ochyra</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7638,11 +7638,6 @@
       <c r="AB60" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7669,10 +7664,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>87809328</v>
+        <v>102209317</v>
       </c>
       <c r="B61" t="n">
-        <v>92870</v>
+        <v>95590</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7681,41 +7676,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2697</v>
+        <v>164</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig tuffmossa</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Palustriella decipiens</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(De Not.) Ochyra</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Milde</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Raudekfjällets SO-sluttning, 500-600 msm, Jmt</t>
+          <t>Raudekfjället, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446811.1227462236</v>
+        <v>446555.937332959</v>
       </c>
       <c r="R61" t="n">
-        <v>7180320.89791601</v>
+        <v>7180283.113254655</v>
       </c>
       <c r="S61" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7739,22 +7745,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7769,22 +7775,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tomas Hallingbäck, Fredrik Larsson, Peter Carlsson, Lars-Åke Flodin</t>
+          <t>Moa Lönneborg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>102209317</v>
+        <v>102638264</v>
       </c>
       <c r="B62" t="n">
-        <v>95590</v>
+        <v>78522</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7797,45 +7803,45 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>164</v>
+        <v>229487</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Fjällgytterlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
+          <t>Pannaria hookeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Milde</t>
+          <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Raudekfjället, Jmt</t>
+          <t>Raudek, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>446555.937332959</v>
+        <v>446802.059622279</v>
       </c>
       <c r="R62" t="n">
-        <v>7180283.113254655</v>
+        <v>7180413.338651118</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7862,22 +7868,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7886,25 +7892,31 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Skifferhällar i fjäll.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Moa Lönneborg</t>
+          <t>Raul Vicente</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Moa Lönneborg</t>
+          <t>Raul Vicente, Robin Isaksson, Måns Svensson, Martin Westberg, Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102638264</v>
+        <v>102679714</v>
       </c>
       <c r="B63" t="n">
         <v>78522</v>
@@ -7937,16 +7949,8 @@
           <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -7955,13 +7959,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>446802.059622279</v>
+        <v>446792.0286411308</v>
       </c>
       <c r="R63" t="n">
-        <v>7180413.338651118</v>
+        <v>7180402.407896792</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8013,30 +8017,25 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Skifferhällar i fjäll.</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Raul Vicente</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Raul Vicente, Robin Isaksson, Måns Svensson, Martin Westberg, Linda Johannesson, Jesper Wadstein</t>
+          <t>Robin Isaksson, Måns Svensson, Raul Vicente</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102679714</v>
+        <v>107467153</v>
       </c>
       <c r="B64" t="n">
-        <v>78522</v>
+        <v>90074</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8045,44 +8044,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229487</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällgytterlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pannaria hookeri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Borrer ex Sm.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Raudek, Jmt</t>
+          <t>Storbäcken norra, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>446792.0286411308</v>
+        <v>447421.5035686882</v>
       </c>
       <c r="R64" t="n">
-        <v>7180402.407896792</v>
+        <v>7179165.853199272</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8106,7 +8102,7 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>2015-08-13</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8116,7 +8112,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>2015-08-13</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8130,29 +8126,32 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Anders Engström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Måns Svensson, Raul Vicente</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>107467153</v>
+        <v>107467154</v>
       </c>
       <c r="B65" t="n">
-        <v>90074</v>
+        <v>103250</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8165,21 +8164,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>221725</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8265,10 +8264,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>107467154</v>
+        <v>111039334</v>
       </c>
       <c r="B66" t="n">
-        <v>103250</v>
+        <v>96350</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8281,37 +8280,49 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>219811</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storbäcken norra, Jmt</t>
+          <t>Leden, Raudekfjället, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447421.5035686882</v>
+        <v>446636.6459318551</v>
       </c>
       <c r="R66" t="n">
-        <v>7179165.853199272</v>
+        <v>7180275.275397192</v>
       </c>
       <c r="S66" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8335,22 +8346,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2015-08-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2015-08-13</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8365,26 +8376,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Engström</t>
+          <t>Jonas Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Via Anders Engström</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
-        </is>
-      </c>
+          <t>Jonas Jonsson, Anders Jonsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111039334</v>
+        <v>112168349</v>
       </c>
       <c r="B67" t="n">
-        <v>96350</v>
+        <v>78705</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8393,53 +8400,44 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219811</v>
+        <v>229487</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fjällgytterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Pannaria hookeri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Leden, Raudekfjället, Frostviken, Jmt</t>
+          <t>raudek, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>446636.6459318551</v>
+        <v>446864</v>
       </c>
       <c r="R67" t="n">
-        <v>7180275.275397192</v>
+        <v>7180422</v>
       </c>
       <c r="S67" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8463,22 +8461,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:42</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:42</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8487,28 +8475,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jonas Jonsson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jonas Jonsson, Anders Jonsson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112168349</v>
+        <v>112786831</v>
       </c>
       <c r="B68" t="n">
-        <v>78705</v>
+        <v>97026</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8517,41 +8506,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229487</v>
+        <v>219795</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällgytterlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pannaria hookeri</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Borrer ex Sm.) Nyl.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>raudek, Jmt</t>
+          <t>Jormliens parkering, 2,7 km NV, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>446864</v>
+        <v>447124</v>
       </c>
       <c r="R68" t="n">
-        <v>7180422</v>
+        <v>7180167</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8578,12 +8564,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8592,29 +8578,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Fjällhed</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112786831</v>
+        <v>112786794</v>
       </c>
       <c r="B69" t="n">
-        <v>97026</v>
+        <v>96091</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8627,21 +8617,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219795</v>
+        <v>222424</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fjällummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lycopodium alpinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8651,10 +8641,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447124</v>
+        <v>447181</v>
       </c>
       <c r="R69" t="n">
-        <v>7180167</v>
+        <v>7180145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8700,7 +8690,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Fjällhed</t>
+          <t>Invid bäck</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8718,10 +8708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112786794</v>
+        <v>112786832</v>
       </c>
       <c r="B70" t="n">
-        <v>96091</v>
+        <v>97031</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8734,21 +8724,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222424</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fjällummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium alpinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8758,10 +8748,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447181</v>
+        <v>447124</v>
       </c>
       <c r="R70" t="n">
-        <v>7180145</v>
+        <v>7180167</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8796,6 +8786,11 @@
           <t>2023-07-19</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>i blom</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8807,7 +8802,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Invid bäck</t>
+          <t>Fjällhed</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112786832</v>
+        <v>112787479</v>
       </c>
       <c r="B71" t="n">
-        <v>97031</v>
+        <v>96170</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8837,38 +8832,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220093</v>
+        <v>222112</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Jormliens parkering, 2,7 km NV, Jmt</t>
+          <t>Raudek-fjället, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447124</v>
+        <v>446877</v>
       </c>
       <c r="R71" t="n">
-        <v>7180167</v>
+        <v>7180418</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8903,11 +8907,6 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>i blom</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8919,7 +8918,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Fjällhed</t>
+          <t>Gräsbevuxen klippavsats</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8937,10 +8936,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112787479</v>
+        <v>112787370</v>
       </c>
       <c r="B72" t="n">
-        <v>96170</v>
+        <v>96097</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8949,47 +8948,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222112</v>
+        <v>224365</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Riplummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Raudek-fjället, Jmt</t>
+          <t>Jormliens parkering, 2,9 km NV, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>446877</v>
+        <v>447093</v>
       </c>
       <c r="R72" t="n">
-        <v>7180418</v>
+        <v>7180233</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9035,7 +9025,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Gräsbevuxen klippavsats</t>
+          <t>Fjällhed</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9053,10 +9043,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112787370</v>
+        <v>112787483</v>
       </c>
       <c r="B73" t="n">
-        <v>96097</v>
+        <v>100070</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9065,38 +9055,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224365</v>
+        <v>1478</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Jormliens parkering, 2,9 km NV, Jmt</t>
+          <t>Raudek-fjället, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447093</v>
+        <v>446877</v>
       </c>
       <c r="R73" t="n">
-        <v>7180233</v>
+        <v>7180418</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9131,6 +9121,11 @@
           <t>2023-07-19</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>ca 100 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9142,7 +9137,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Fjällhed</t>
+          <t>Fuktig, brant klipphäll</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9160,10 +9155,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112787483</v>
+        <v>112787563</v>
       </c>
       <c r="B74" t="n">
-        <v>100070</v>
+        <v>96353</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9172,25 +9167,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1478</v>
+        <v>222759</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9238,11 +9233,6 @@
           <t>2023-07-19</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>ca 100 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9254,7 +9244,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Fuktig, brant klipphäll</t>
+          <t>Gräsbevuxen klippavsats</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9272,10 +9262,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112787563</v>
+        <v>112787476</v>
       </c>
       <c r="B75" t="n">
-        <v>96353</v>
+        <v>96169</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9284,28 +9274,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222759</v>
+        <v>164</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Milde</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Raudek-fjället, Jmt</t>
@@ -9379,10 +9378,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112787476</v>
+        <v>112787366</v>
       </c>
       <c r="B76" t="n">
-        <v>96169</v>
+        <v>96353</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9391,47 +9390,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>164</v>
+        <v>222759</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Milde</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Raudek-fjället, Jmt</t>
+          <t>Jormliens parkering, 2,9 km NV, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>446877</v>
+        <v>447093</v>
       </c>
       <c r="R76" t="n">
-        <v>7180418</v>
+        <v>7180233</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9477,7 +9467,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Gräsbevuxen klippavsats</t>
+          <t>Fjällhed</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9495,10 +9485,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112787366</v>
+        <v>112787550</v>
       </c>
       <c r="B77" t="n">
-        <v>96353</v>
+        <v>100070</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9507,38 +9497,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222759</v>
+        <v>1478</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Jormliens parkering, 2,9 km NV, Jmt</t>
+          <t>Raudek-fjället, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447093</v>
+        <v>446460</v>
       </c>
       <c r="R77" t="n">
-        <v>7180233</v>
+        <v>7180250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9584,7 +9583,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Fjällhed</t>
+          <t>Fuktig, brant klipphäll</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9602,10 +9601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112787550</v>
+        <v>113642907</v>
       </c>
       <c r="B78" t="n">
-        <v>100070</v>
+        <v>93777</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9614,47 +9613,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1478</v>
+        <v>2265</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Klibbig fetknopp</t>
+          <t>Kärrtrumpetmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sedum villosum</t>
+          <t>Tayloria lingulata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Raudek-fjället, Jmt</t>
+          <t>Raudek, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>446460</v>
+        <v>446832</v>
       </c>
       <c r="R78" t="n">
-        <v>7180250</v>
+        <v>7180421</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9681,12 +9675,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9695,33 +9689,43 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Fuktig, brant klipphäll</t>
-        </is>
-      </c>
-      <c r="AT78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Lars Hedenäs</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113642907</v>
+        <v>114053035</v>
       </c>
       <c r="B79" t="n">
-        <v>93777</v>
+        <v>96687</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9730,29 +9734,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2265</v>
+        <v>164</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kärrtrumpetmossa</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tayloria lingulata</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Dicks.) Lindb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>Milde</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
@@ -9762,10 +9774,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>446832</v>
+        <v>446883</v>
       </c>
       <c r="R79" t="n">
-        <v>7180421</v>
+        <v>7180409</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9810,39 +9822,25 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>Lars Hedenäs</t>
-        </is>
-      </c>
-      <c r="AT79" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
+      <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>114053035</v>
+        <v>117780812</v>
       </c>
       <c r="B80" t="n">
-        <v>96687</v>
+        <v>96786</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9851,50 +9849,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>164</v>
+        <v>224360</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordlåsbräken</t>
+          <t>Gul groddlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Botrychium boreale</t>
+          <t>Huperzia arctica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Milde</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>(Grossh. ex Tolm.) Sipliv.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Raudek, Jmt</t>
+          <t>Jormliens parkering, 2,7 km NV, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>446883</v>
+        <v>447181</v>
       </c>
       <c r="R80" t="n">
-        <v>7180409</v>
+        <v>7180145</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9921,12 +9907,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9935,29 +9921,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Fjällhed</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117780812</v>
+        <v>118377994</v>
       </c>
       <c r="B81" t="n">
-        <v>96786</v>
+        <v>79529</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9966,41 +9956,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>224360</v>
+        <v>229487</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gul groddlummer</t>
+          <t>Fjällgytterlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Huperzia arctica</t>
+          <t>Pannaria hookeri</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Grossh. ex Tolm.) Sipliv.</t>
+          <t>(Borrer ex Sm.) Nyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Jormliens parkering, 2,7 km NV, Jmt</t>
+          <t>Raudekfjället, SO-sluttningen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447181</v>
+        <v>446804</v>
       </c>
       <c r="R81" t="n">
-        <v>7180145</v>
+        <v>7180398</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10024,12 +10014,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>12 bålar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10038,33 +10033,34 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Fjällhed</t>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>stenhäll</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118377994</v>
+        <v>118377997</v>
       </c>
       <c r="B82" t="n">
-        <v>79529</v>
+        <v>97071</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10073,25 +10069,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229487</v>
+        <v>222759</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fjällgytterlav</t>
+          <t>Taggbräken</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pannaria hookeri</t>
+          <t>Polystichum lonchitis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Borrer ex Sm.) Nyl.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10101,10 +10097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>446804</v>
+        <v>446813</v>
       </c>
       <c r="R82" t="n">
-        <v>7180398</v>
+        <v>7180423</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10139,25 +10135,14 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>12 bålar</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>stenhäll</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10174,10 +10159,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118377997</v>
+        <v>118378004</v>
       </c>
       <c r="B83" t="n">
-        <v>97071</v>
+        <v>78847</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10186,25 +10171,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222759</v>
+        <v>1321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Taggbräken</t>
+          <t>Klot-tegellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Polystichum lonchitis</t>
+          <t>Psora globifera</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Ach.) A.Massal.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10214,10 +10199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>446813</v>
+        <v>446886</v>
       </c>
       <c r="R83" t="n">
-        <v>7180423</v>
+        <v>7180480</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10252,6 +10237,11 @@
           <t>2022-07-29</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>1 kv.dm inom en halv kvadratmeterruta</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10260,6 +10250,11 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>brant lodyta mot SO</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10276,10 +10271,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118378004</v>
+        <v>118378548</v>
       </c>
       <c r="B84" t="n">
-        <v>78847</v>
+        <v>100810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10288,25 +10283,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1321</v>
+        <v>1478</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klot-tegellav</t>
+          <t>Klibbig fetknopp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Psora globifera</t>
+          <t>Sedum villosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10316,10 +10311,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>446886</v>
+        <v>446870</v>
       </c>
       <c r="R84" t="n">
-        <v>7180480</v>
+        <v>7180413</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10354,11 +10349,6 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>1 kv.dm inom en halv kvadratmeterruta</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10367,11 +10357,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>brant lodyta mot SO</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10385,108 +10370,6 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>118378548</v>
-      </c>
-      <c r="B85" t="n">
-        <v>100810</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>1478</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Klibbig fetknopp</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Sedum villosum</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Raudekfjället, SO-sluttningen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>446870</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7180413</v>
-      </c>
-      <c r="S85" t="n">
-        <v>25</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Martin Westberg</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Martin Westberg</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13357-2023 artfynd.xlsx
+++ b/artfynd/A 13357-2023 artfynd.xlsx
@@ -10376,7 +10376,7 @@
         <v>127012956</v>
       </c>
       <c r="B85" t="n">
-        <v>101237</v>
+        <v>101312</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>127013048</v>
       </c>
       <c r="B86" t="n">
-        <v>98265</v>
+        <v>98340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>127138390</v>
       </c>
       <c r="B87" t="n">
-        <v>97305</v>
+        <v>97380</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127138381</v>
       </c>
       <c r="B88" t="n">
-        <v>101237</v>
+        <v>101312</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
